--- a/feedback_forms/013_faculty_live_demo_feedback--feedback_forms.xlsx
+++ b/feedback_forms/013_faculty_live_demo_feedback--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>demo_rated</t>
+          <t>presenter_rating</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What did you rate</t>
+          <t>What did you rate the presenter's performance?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What do you think</t>
+          <t>What were your thoughts on the presentation?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How effective was the presenter</t>
+          <t>How effective was the presenter?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>suggestions_for_improvement</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Do you have any suggestions for improvement</t>
+          <t>Do you have any suggestions for improvement?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>comments_phone_number</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Comments phone number</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>suggestions_for_improvement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Suggestion for improvement</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comments_email</t>
+          <t>comments_phone_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Comments email</t>
+          <t>Comments Phone 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>comments_phone_number</t>
+          <t>comments_from_phone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comments phone number</t>
+          <t>Comments from phone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>comments_to_phone</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Comments to phone</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,269 +842,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>comments_to_email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Comments to email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>comments_from_phone</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Comments from phone</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>comments_to_phone</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Comments to phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>comments_to_email</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Comments to email</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>comments_from_phone</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comments from phone</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>comments_email</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Comments email</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>comments_phone_number</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Comments phone number</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1121,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1149,7 +896,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>presenter_effectiveness_choices</t>
+          <t>presenter_rating_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1166,7 +913,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>presenter_effectiveness_choices</t>
+          <t>presenter_rating_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1183,7 +930,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>presenter_effectiveness_choices</t>
+          <t>presenter_rating_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1200,15 +947,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>presenter_rating_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>presenter_effectiveness_choices</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>presenter_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>presenter_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>presenter_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>poor</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Poor</t>
         </is>
